--- a/data/trans_dic/P0901-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 19,43</t>
+          <t>14,94; 19,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,92; 27,63</t>
+          <t>22,19; 28,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 26,25</t>
+          <t>20,05; 26,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,93</t>
+          <t>26,16; 33,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 28,98</t>
+          <t>23,95; 28,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,58; 39,95</t>
+          <t>34,77; 40,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,24; 40,43</t>
+          <t>33,57; 40,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,92; 46,62</t>
+          <t>40,85; 46,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,52; 23,98</t>
+          <t>20,83; 24,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,99; 34,04</t>
+          <t>30,28; 34,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,73; 33,43</t>
+          <t>28,62; 33,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 40,59</t>
+          <t>35,97; 40,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,82</t>
+          <t>4,53; 6,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,37</t>
+          <t>5,95; 8,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,5</t>
+          <t>6,02; 8,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,58</t>
+          <t>7,78; 12,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 11,77</t>
+          <t>8,71; 11,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 13,2</t>
+          <t>9,95; 13,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 14,85</t>
+          <t>11,64; 14,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,38</t>
+          <t>9,99; 15,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,65</t>
+          <t>6,89; 8,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 10,27</t>
+          <t>8,29; 10,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,24</t>
+          <t>9,32; 11,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,42</t>
+          <t>9,71; 13,54</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,62</t>
+          <t>2,88; 6,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,13</t>
+          <t>4,18; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,94</t>
+          <t>3,74; 8,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,38</t>
+          <t>6,18; 10,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,34</t>
+          <t>6,7; 11,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,91</t>
+          <t>5,87; 11,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,15</t>
+          <t>7,66; 13,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,74</t>
+          <t>7,73; 11,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,31</t>
+          <t>5,19; 8,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,33</t>
+          <t>5,51; 9,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,98</t>
+          <t>6,13; 9,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,18</t>
+          <t>7,41; 10,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 10,11</t>
+          <t>8,08; 10,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,19</t>
+          <t>10,95; 13,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 11,64</t>
+          <t>9,42; 11,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,61</t>
+          <t>10,15; 14,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 17,65</t>
+          <t>15,11; 17,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 22,32</t>
+          <t>19,39; 22,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 20,7</t>
+          <t>17,95; 20,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 20,64</t>
+          <t>15,91; 20,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 13,66</t>
+          <t>11,95; 13,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,6; 17,38</t>
+          <t>15,57; 17,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,25; 16,1</t>
+          <t>14,26; 16,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 17,28</t>
+          <t>14,02; 17,3</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>153724; 200432</t>
+          <t>154128; 203324</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>213626; 269322</t>
+          <t>216316; 274009</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150750; 198043</t>
+          <t>151230; 198601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135790; 174734</t>
+          <t>134722; 173521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>318344; 381182</t>
+          <t>314913; 380646</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>462627; 534480</t>
+          <t>465181; 538826</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>340528; 402153</t>
+          <t>333932; 402639</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>309117; 352254</t>
+          <t>308603; 352284</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>481504; 562730</t>
+          <t>488756; 571417</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>693472; 787134</t>
+          <t>700107; 790395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>502412; 584659</t>
+          <t>500632; 580344</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>457011; 515617</t>
+          <t>456944; 514256</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76878; 115419</t>
+          <t>76760; 114546</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117621; 164348</t>
+          <t>116827; 164174</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128827; 176550</t>
+          <t>124914; 175125</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165469; 287869</t>
+          <t>177951; 287960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>139135; 186886</t>
+          <t>138316; 184467</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>177002; 231977</t>
+          <t>174864; 232809</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>232299; 295290</t>
+          <t>231408; 294273</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>209961; 343830</t>
+          <t>223293; 344841</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>223670; 283976</t>
+          <t>226036; 284839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>305132; 382134</t>
+          <t>308682; 381413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>371561; 456831</t>
+          <t>378935; 459956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>429461; 607182</t>
+          <t>439261; 612796</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16070; 36477</t>
+          <t>15854; 36576</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18932; 43936</t>
+          <t>20117; 44555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19672; 43424</t>
+          <t>20438; 44564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38934; 67097</t>
+          <t>39983; 67840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31915; 58767</t>
+          <t>31925; 56073</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26240; 50043</t>
+          <t>26905; 50983</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42129; 72189</t>
+          <t>42058; 72767</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51403; 77566</t>
+          <t>51041; 76420</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53632; 85374</t>
+          <t>53349; 86624</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53167; 87689</t>
+          <t>51802; 86271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67880; 109358</t>
+          <t>67192; 105478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96325; 133099</t>
+          <t>96900; 133201</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>264385; 331126</t>
+          <t>264894; 336158</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>372282; 450961</t>
+          <t>374545; 453130</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>319653; 393309</t>
+          <t>318196; 392332</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>352156; 504126</t>
+          <t>350293; 499091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>507095; 596362</t>
+          <t>510656; 594358</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>694658; 793403</t>
+          <t>689232; 792066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>637432; 731246</t>
+          <t>634081; 738150</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>568506; 753811</t>
+          <t>580937; 760897</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>795998; 909314</t>
+          <t>795588; 900460</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1087931; 1212123</t>
+          <t>1085845; 1208330</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>984439; 1112265</t>
+          <t>985365; 1106077</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>991597; 1227432</t>
+          <t>996026; 1228276</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0901-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 19,71</t>
+          <t>15,05; 19,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,19; 28,11</t>
+          <t>22,01; 28,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,05; 26,33</t>
+          <t>20,41; 26,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,16; 33,7</t>
+          <t>25,07; 32,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,95; 28,94</t>
+          <t>23,99; 28,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,77; 40,28</t>
+          <t>34,75; 40,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,57; 40,48</t>
+          <t>33,6; 40,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,85; 46,63</t>
+          <t>40,53; 46,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,83; 24,35</t>
+          <t>20,88; 24,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,28; 34,18</t>
+          <t>29,97; 34,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,62; 33,18</t>
+          <t>28,63; 33,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 40,48</t>
+          <t>34,82; 39,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,76</t>
+          <t>4,62; 6,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,36</t>
+          <t>5,94; 8,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,43</t>
+          <t>6,17; 8,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,58</t>
+          <t>10,37; 13,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,62</t>
+          <t>8,56; 11,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,24</t>
+          <t>10,22; 13,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 14,8</t>
+          <t>11,77; 14,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 15,42</t>
+          <t>14,29; 17,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 8,68</t>
+          <t>6,9; 8,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 10,25</t>
+          <t>8,28; 10,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 11,32</t>
+          <t>9,17; 11,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,54</t>
+          <t>12,6; 14,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,63</t>
+          <t>3,0; 6,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,26</t>
+          <t>4,33; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,15</t>
+          <t>3,53; 7,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,49</t>
+          <t>5,77; 10,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,77</t>
+          <t>6,58; 12,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,12</t>
+          <t>5,39; 10,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 13,25</t>
+          <t>7,62; 12,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,57</t>
+          <t>8,58; 12,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,43</t>
+          <t>5,22; 8,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,18</t>
+          <t>5,61; 9,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,62</t>
+          <t>6,07; 9,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,19</t>
+          <t>7,69; 10,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 10,26</t>
+          <t>8,13; 10,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 13,25</t>
+          <t>10,87; 13,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 11,62</t>
+          <t>9,45; 11,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 14,47</t>
+          <t>12,46; 14,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 17,59</t>
+          <t>15,08; 17,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,39; 22,29</t>
+          <t>19,53; 22,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 20,9</t>
+          <t>18,16; 21,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 20,83</t>
+          <t>19,57; 21,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 13,53</t>
+          <t>11,95; 13,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 17,33</t>
+          <t>15,59; 17,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 16,01</t>
+          <t>14,2; 15,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 17,3</t>
+          <t>16,47; 18,07</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153717</t>
+          <t>164617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>330965</t>
+          <t>355578</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>484683</t>
+          <t>520195</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>154128; 203324</t>
+          <t>155294; 204371</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>216316; 274009</t>
+          <t>214514; 273270</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151230; 198601</t>
+          <t>153943; 197563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134722; 173521</t>
+          <t>145016; 186016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>314913; 380646</t>
+          <t>315556; 380203</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>465181; 538826</t>
+          <t>464923; 536256</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>333932; 402639</t>
+          <t>334166; 398693</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>308603; 352284</t>
+          <t>333167; 378863</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>488756; 571417</t>
+          <t>489958; 566418</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>700107; 790395</t>
+          <t>692952; 787658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>500632; 580344</t>
+          <t>500721; 580375</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>456944; 514256</t>
+          <t>487643; 551178</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244005</t>
+          <t>261791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>298337</t>
+          <t>338134</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>542342</t>
+          <t>599926</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76760; 114546</t>
+          <t>78254; 115584</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116827; 164174</t>
+          <t>116743; 161864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124914; 175125</t>
+          <t>128115; 176197</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177951; 287960</t>
+          <t>231163; 296148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>138316; 184467</t>
+          <t>135870; 186923</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>174864; 232809</t>
+          <t>179596; 236097</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>231408; 294273</t>
+          <t>234014; 297713</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>223293; 344841</t>
+          <t>310037; 368902</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>226036; 284839</t>
+          <t>226409; 287520</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>308682; 381413</t>
+          <t>308084; 382813</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>378935; 459956</t>
+          <t>372765; 454835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>439261; 612796</t>
+          <t>554241; 647662</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50997</t>
+          <t>54594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>76432</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>114178</t>
+          <t>131027</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15854; 36576</t>
+          <t>16536; 36919</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20117; 44555</t>
+          <t>20855; 44560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20438; 44564</t>
+          <t>19281; 43506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39983; 67840</t>
+          <t>41026; 71524</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31925; 56073</t>
+          <t>31357; 57903</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26905; 50983</t>
+          <t>24740; 50025</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42058; 72767</t>
+          <t>41864; 70660</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51041; 76420</t>
+          <t>63039; 91055</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53349; 86624</t>
+          <t>53605; 85870</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51802; 86271</t>
+          <t>52679; 87083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67192; 105478</t>
+          <t>66493; 103594</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96900; 133201</t>
+          <t>111295; 153257</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>448720</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>692484</t>
+          <t>770145</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1141203</t>
+          <t>1251147</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>264894; 336158</t>
+          <t>266224; 332220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>374545; 453130</t>
+          <t>371617; 453255</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>318196; 392332</t>
+          <t>319082; 394421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>350293; 499091</t>
+          <t>438477; 522035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>510656; 594358</t>
+          <t>509670; 596973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>689232; 792066</t>
+          <t>694043; 789437</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>634081; 738150</t>
+          <t>641534; 742345</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>580937; 760897</t>
+          <t>729379; 809418</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>795588; 900460</t>
+          <t>795572; 901563</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1085845; 1208330</t>
+          <t>1087097; 1214532</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>985365; 1106077</t>
+          <t>981420; 1103965</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>996026; 1228276</t>
+          <t>1193553; 1308922</t>
         </is>
       </c>
     </row>
